--- a/storage/app/reports/Sample Performance Report MIDTASK.xlsx
+++ b/storage/app/reports/Sample Performance Report MIDTASK.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\MPA FILES\PA 210 - Capstone (Encarnacion)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TheMidTaskApp\server\storage\app\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B3D845-94B6-4CF6-8DA8-8B79ED37F107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3543D437-C71F-4474-8231-C981A549207C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CF2489E5-7EF6-4E73-9722-D0BD52CD0B6B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{CF2489E5-7EF6-4E73-9722-D0BD52CD0B6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,30 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t>Division of Zamboanga del Sur</t>
   </si>
@@ -81,12 +59,6 @@
     <t>PERIOD COVERED:</t>
   </si>
   <si>
-    <t>(Admin Officer)</t>
-  </si>
-  <si>
-    <t>(ex: January 1, 2026 - December 31, 2026)</t>
-  </si>
-  <si>
     <t>____________________________</t>
   </si>
   <si>
@@ -156,12 +128,6 @@
     <t>POSITION</t>
   </si>
   <si>
-    <t>(Printing/Generated Date and Time)</t>
-  </si>
-  <si>
-    <t>Date &amp; Time: _____________</t>
-  </si>
-  <si>
     <t>(Page 2 of ___)</t>
   </si>
   <si>
@@ -207,13 +173,10 @@
     <t>Unsatisfactory</t>
   </si>
   <si>
-    <t>Outsatnding</t>
-  </si>
-  <si>
-    <t>(Assignment - AO)</t>
-  </si>
-  <si>
     <t>Performance Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date &amp; Time: </t>
   </si>
 </sst>
 </file>
@@ -223,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,13 +227,6 @@
       <color theme="1"/>
       <name val="Baskerville Old Face"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="7"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -397,7 +353,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -412,15 +368,86 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -432,89 +459,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -638,7 +592,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6644640" y="2576331"/>
+          <a:off x="7741920" y="2576331"/>
           <a:ext cx="3860554" cy="1092988"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1297,324 +1251,322 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+    </row>
+    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+    </row>
+    <row r="11" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="41" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+    </row>
+    <row r="13" spans="2:8" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="E13" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="35"/>
+      <c r="G15" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="35"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="31"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="37"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="31"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="E13" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
+      <c r="C18" s="37"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="23"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="17" t="s">
+      <c r="C21" s="32"/>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="32"/>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="24">
-        <v>4.5</v>
-      </c>
-      <c r="F16" s="25"/>
-      <c r="G16" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="23"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="24">
-        <v>4.2</v>
-      </c>
-      <c r="F17" s="25"/>
-      <c r="G17" s="22" t="s">
+      <c r="G22" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="F24" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="F25" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="23"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="24">
-        <v>4.37</v>
-      </c>
-      <c r="F18" s="25"/>
-      <c r="G18" s="22" t="str">
-        <f>G17</f>
-        <v>Very Satisfactory</v>
-      </c>
-      <c r="H18" s="23"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="41" cm="1">
-        <f t="array" ref="E19">SUM(E16:F18/3)</f>
-        <v>4.3566666666666674</v>
-      </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="15" t="str">
-        <f>G18</f>
-        <v>Very Satisfactory</v>
-      </c>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="20"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="20"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="43" t="s">
+      <c r="G25" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" s="20"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="F24" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="G24" s="44" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="F25" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="G25" s="44" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L31" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" s="9"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="26"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="26"/>
+      <c r="C43" s="9"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>32</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C45" s="9"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H47" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="B50" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="39"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="26" t="s">
+      <c r="B50" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="27"/>
+      <c r="E51" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B51" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="10" t="s">
+      <c r="F51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="10"/>
-      <c r="E51" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="14" t="s">
+      <c r="H51" s="27"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B52" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G51" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" s="10"/>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" s="29">
+      <c r="C52" s="18">
         <v>1</v>
       </c>
-      <c r="D52" s="29"/>
-      <c r="E52" s="30">
+      <c r="D52" s="18"/>
+      <c r="E52" s="12">
         <v>2</v>
       </c>
-      <c r="F52" s="30">
+      <c r="F52" s="12">
         <v>2</v>
       </c>
-      <c r="G52" s="31">
+      <c r="G52" s="28">
         <f>C52/E52</f>
         <v>0.5</v>
       </c>
-      <c r="H52" s="31"/>
+      <c r="H52" s="28"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C53" s="29">
+      <c r="B53" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="18">
         <v>10</v>
       </c>
-      <c r="D53" s="29"/>
-      <c r="E53" s="30">
+      <c r="D53" s="18"/>
+      <c r="E53" s="12">
         <v>12</v>
       </c>
-      <c r="F53" s="30">
+      <c r="F53" s="12">
         <v>12</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="29">
         <f>(C53/E53)</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="H53" s="33"/>
+      <c r="H53" s="29"/>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B54" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
+      <c r="B54" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H57" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="27"/>
-      <c r="C61" s="26"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="9"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="27"/>
-      <c r="C62" s="26"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="9"/>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C64" s="26"/>
+      <c r="C64" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="30">
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="C54:D54"/>
     <mergeCell ref="G54:H54"/>
     <mergeCell ref="B50:H50"/>
@@ -1627,21 +1579,6 @@
     <mergeCell ref="C53:D53"/>
     <mergeCell ref="G52:H52"/>
     <mergeCell ref="G53:H53"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/storage/app/reports/Sample Performance Report MIDTASK.xlsx
+++ b/storage/app/reports/Sample Performance Report MIDTASK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TheMidTaskApp\server\storage\app\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3543D437-C71F-4474-8231-C981A549207C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD32C66-E45B-44D7-9A71-A97FBE14FADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{CF2489E5-7EF6-4E73-9722-D0BD52CD0B6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Division of Zamboanga del Sur</t>
   </si>
@@ -101,9 +101,6 @@
     <t>BREAKDOWN ANALYSIS</t>
   </si>
   <si>
-    <t>(not yet sure sa term)</t>
-  </si>
-  <si>
     <t>(3)</t>
   </si>
   <si>
@@ -138,9 +135,6 @@
   </si>
   <si>
     <t>Remarks</t>
-  </si>
-  <si>
-    <t>INCLUDE  content description in the Printable Report (Depende na unsaon pag layout?)</t>
   </si>
   <si>
     <t>Range</t>
@@ -353,24 +347,9 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -387,25 +366,19 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -426,28 +399,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -459,13 +460,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -556,350 +560,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>69351</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>462034</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>65059</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{923ADC3D-DB5F-2CAE-27D6-13BFB6A0455F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7741920" y="2576331"/>
-          <a:ext cx="3860554" cy="1092988"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="Straight Arrow Connector 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF541F35-1BC5-BA3B-9464-7CDF082C7937}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5227320" y="3147060"/>
-          <a:ext cx="1333500" cy="15240"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EB05AE9-7E6C-8737-01B6-1FC761EF0F3C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5234940" y="3307080"/>
-          <a:ext cx="1356360" cy="45720"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="Straight Arrow Connector 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69255030-18FF-B382-577B-8B581B1C5BE0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5219700" y="2933700"/>
-          <a:ext cx="1348740" cy="15240"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>594359</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A20F20E-6DF4-D9C3-A598-006250382150}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="556260" y="4937760"/>
-          <a:ext cx="4503419" cy="1897380"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="Straight Arrow Connector 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2E188A2-A3A1-41F9-94BF-474033EEE78F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5173980" y="5707380"/>
-          <a:ext cx="2278380" cy="30480"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>434340</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>22245</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>147904</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>8045</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1BA81F2-FE08-8635-178E-5268054A9B61}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6118860" y="9341505"/>
-          <a:ext cx="5199964" cy="1814600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1222,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4400D0-9C61-4258-B547-D08FC28B3CEE}">
-  <dimension ref="B3:L64"/>
+  <dimension ref="B3:K64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1232,325 +892,358 @@
     <col min="7" max="7" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D3" s="1"/>
-      <c r="E3" s="2" t="s">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C3" s="43" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="D4" s="1"/>
-      <c r="E4" s="3" t="s">
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="2:11" ht="15" x14ac:dyDescent="0.35">
+      <c r="C4" s="44" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D5" s="1"/>
-      <c r="E5" s="4" t="s">
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C5" s="45" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+    </row>
+    <row r="9" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-    </row>
-    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+    </row>
+    <row r="10" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-    </row>
-    <row r="11" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+    </row>
+    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-    </row>
-    <row r="13" spans="2:8" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="E13" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="33" t="s">
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+    </row>
+    <row r="13" spans="2:11" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="B13" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="33" t="s">
+      <c r="C15" s="38"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="35"/>
-      <c r="G15" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="35"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="36" t="s">
+      <c r="F15" s="33"/>
+      <c r="G15" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="33"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="31"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="36" t="s">
+      <c r="C16" s="40"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="37"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="31"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="36" t="s">
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="37"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="31"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="23"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="32" t="s">
+      <c r="C18" s="40"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="32"/>
+      <c r="C21" s="21"/>
       <c r="D21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="32" t="s">
+      <c r="F21" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="32"/>
+      <c r="C22" s="21"/>
       <c r="D22" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="32" t="s">
+      <c r="F22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="32"/>
+      <c r="C23" s="21"/>
       <c r="D23" t="s">
         <v>17</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F24" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="F24" s="17" t="s">
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F25" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G25" s="3" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="F25" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="L31" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="23" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="15" t="s">
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="9"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="9"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="9"/>
+        <v>44</v>
+      </c>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="9" t="s">
-        <v>21</v>
-      </c>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="4"/>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C51" s="27" t="s">
+      <c r="C51" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="27"/>
-      <c r="E51" s="7" t="s">
+      <c r="D51" s="20"/>
+      <c r="E51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" s="27" t="s">
+      <c r="G51" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H51" s="27"/>
+      <c r="H51" s="20"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" s="18">
+      <c r="B52" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="25">
         <v>1</v>
       </c>
-      <c r="D52" s="18"/>
-      <c r="E52" s="12">
+      <c r="D52" s="25"/>
+      <c r="E52" s="7">
         <v>2</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="7">
         <v>2</v>
       </c>
-      <c r="G52" s="28">
+      <c r="G52" s="29">
         <f>C52/E52</f>
         <v>0.5</v>
       </c>
-      <c r="H52" s="28"/>
+      <c r="H52" s="29"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C53" s="18">
+      <c r="B53" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="25">
         <v>10</v>
       </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="12">
+      <c r="D53" s="25"/>
+      <c r="E53" s="7">
         <v>12</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="7">
         <v>12</v>
       </c>
-      <c r="G53" s="29">
+      <c r="G53" s="30">
         <f>(C53/E53)</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="H53" s="29"/>
+      <c r="H53" s="30"/>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B54" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
+      <c r="B54" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="10"/>
-      <c r="C61" s="9"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="4"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="10"/>
-      <c r="C62" s="9"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="4"/>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C64" s="9"/>
+      <c r="C64" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="37">
+    <mergeCell ref="C5:F5"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="E16:F16"/>
@@ -1564,21 +1257,25 @@
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B13:I13"/>
     <mergeCell ref="C54:D54"/>
     <mergeCell ref="G54:H54"/>
     <mergeCell ref="B50:H50"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="G53:H53"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="G51:H51"/>
     <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="C45:F45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
